--- a/jpcore-r4b/develop/StructureDefinition-jp-medicationrequest.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-medicationrequest.xlsx
@@ -69,7 +69,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) (http://jpfhir.jp, office@hlfhir.jp)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/jpcore-r4b/develop/StructureDefinition-jp-medicationrequest.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-medicationrequest.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4140" uniqueCount="669">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4140" uniqueCount="672">
   <si>
     <t>Property</t>
   </si>
@@ -1520,13 +1520,19 @@
 </t>
   </si>
   <si>
-    <t>薬の服用方法・服用した方法、または服用すべき方法</t>
+    <t>How the medication should be taken</t>
+  </si>
+  <si>
+    <t>Indicates how the medication is to be used by the patient.</t>
   </si>
   <si>
     <t>There are examples where a medication request may include the option of an oral dose or an Intravenous or Intramuscular dose.  For example, "Ondansetron 8mg orally or IV twice a day as needed for nausea" or "Compazine® (prochlorperazine) 5-10mg PO or 25mg PR bid prn nausea or vomiting".  In these cases, two medication requests would be created that could be grouped together.  The decision on which dose and route of administration to use is based on the patient's condition at the time the dose is needed.</t>
   </si>
   <si>
-    <t>.outboundRelationship[typeCode=COMP].target[classCode=SBADM, moodCode=INT]</t>
+    <t>Request.occurrence[x]</t>
+  </si>
+  <si>
+    <t>see dosageInstruction mapping</t>
   </si>
   <si>
     <t>MedicationRequest.dispenseRequest</t>
@@ -1667,14 +1673,7 @@
     <t>このエレメントはどのような量を表現するか定義するためにコンテキストにあわせてよく定義される。したがって、どのような単位でも利用することができる。使用されるコンテキストによってcomparatorエレメントで値が定義されることもある。</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
-qty-3:If a code for the unit is present, the system SHALL also be present {code.empty() or system.exists()}sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
-  </si>
-  <si>
-    <t>PQ, IVL&lt;PQ&gt;, MO, CO, depending on the values</t>
-  </si>
-  <si>
-    <t>SN (see also Range) or CQ</t>
+    <t>Supply.quantity[moodCode=RQO]</t>
   </si>
   <si>
     <t>MedicationRequest.dispenseRequest.initialFill.duration</t>
@@ -1810,6 +1809,15 @@
   </si>
   <si>
     <t>1回の調剤で払い出される薬剤の量</t>
+  </si>
+  <si>
+    <t>Message/Body/NewRx/MedicationPrescribed/DaysSupply</t>
+  </si>
+  <si>
+    <t>quantity</t>
+  </si>
+  <si>
+    <t>RXD-4-Actual Dispense Amount / RXD-5.1-Actual Dispense Units.code / RXD-5.3-Actual Dispense Units.name of coding system</t>
   </si>
   <si>
     <t>MedicationRequest.dispenseRequest.expectedSupplyDuration</t>
@@ -10914,10 +10922,10 @@
         <v>478</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10982,13 +10990,13 @@
         <v>104</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>82</v>
+        <v>481</v>
       </c>
       <c r="AL73" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>82</v>
@@ -10999,10 +11007,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11025,13 +11033,13 @@
         <v>82</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -11082,7 +11090,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11094,16 +11102,16 @@
         <v>82</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>82</v>
@@ -11114,10 +11122,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11143,10 +11151,10 @@
         <v>214</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -11229,10 +11237,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11258,10 +11266,10 @@
         <v>139</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -11342,13 +11350,13 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="C77" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="D77" t="s" s="2">
         <v>82</v>
@@ -11370,13 +11378,13 @@
         <v>82</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11436,10 +11444,10 @@
         <v>81</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>82</v>
@@ -11459,13 +11467,13 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="D78" t="s" s="2">
         <v>82</v>
@@ -11487,13 +11495,13 @@
         <v>82</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11553,10 +11561,10 @@
         <v>81</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>82</v>
@@ -11576,14 +11584,14 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
@@ -11605,10 +11613,10 @@
         <v>139</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="N79" t="s" s="2">
         <v>142</v>
@@ -11663,7 +11671,7 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -11695,10 +11703,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11721,16 +11729,16 @@
         <v>82</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -11780,7 +11788,7 @@
         <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -11792,7 +11800,7 @@
         <v>82</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>82</v>
@@ -11801,7 +11809,7 @@
         <v>82</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>82</v>
@@ -11812,10 +11820,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11927,10 +11935,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12044,14 +12052,14 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
@@ -12073,10 +12081,10 @@
         <v>139</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="N83" t="s" s="2">
         <v>142</v>
@@ -12131,7 +12139,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12163,10 +12171,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12189,16 +12197,16 @@
         <v>82</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12248,7 +12256,7 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12257,10 +12265,10 @@
         <v>92</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>499</v>
+        <v>82</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>524</v>
+        <v>104</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>82</v>
@@ -12269,13 +12277,13 @@
         <v>82</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>526</v>
+        <v>82</v>
       </c>
     </row>
     <row r="85">
@@ -12315,7 +12323,7 @@
         <v>530</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12432,7 +12440,7 @@
         <v>534</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -13244,7 +13252,7 @@
         <v>82</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="L93" t="s" s="2">
         <v>569</v>
@@ -13253,7 +13261,7 @@
         <v>570</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -13312,33 +13320,33 @@
         <v>92</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>499</v>
+        <v>82</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>524</v>
+        <v>104</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>82</v>
+        <v>571</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>525</v>
+        <v>572</v>
       </c>
       <c r="AN93" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>526</v>
+        <v>573</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13364,13 +13372,13 @@
         <v>528</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -13420,7 +13428,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13438,10 +13446,10 @@
         <v>82</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>82</v>
@@ -13452,10 +13460,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13567,10 +13575,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13684,10 +13692,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13710,19 +13718,19 @@
         <v>93</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>82</v>
@@ -13771,7 +13779,7 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -13792,21 +13800,21 @@
         <v>82</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="AN97" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>587</v>
+        <v>590</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13832,20 +13840,20 @@
         <v>112</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" t="s" s="2">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q98" t="s" s="2">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="R98" t="s" s="2">
         <v>82</v>
@@ -13870,7 +13878,7 @@
       </c>
       <c r="Y98" s="2"/>
       <c r="Z98" t="s" s="2">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>82</v>
@@ -13888,7 +13896,7 @@
         <v>82</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -13909,21 +13917,21 @@
         <v>82</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="AN98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>596</v>
+        <v>599</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13949,21 +13957,21 @@
         <v>214</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" t="s" s="2">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q99" s="2"/>
       <c r="R99" t="s" s="2">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="S99" t="s" s="2">
         <v>82</v>
@@ -14005,7 +14013,7 @@
         <v>82</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -14026,21 +14034,21 @@
         <v>82</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="AN99" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO99" t="s" s="2">
-        <v>604</v>
+        <v>607</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14066,21 +14074,21 @@
         <v>106</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" t="s" s="2">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q100" s="2"/>
       <c r="R100" t="s" s="2">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="S100" t="s" s="2">
         <v>82</v>
@@ -14122,7 +14130,7 @@
         <v>82</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14131,7 +14139,7 @@
         <v>92</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="AJ100" t="s" s="2">
         <v>104</v>
@@ -14143,21 +14151,21 @@
         <v>82</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>604</v>
+        <v>607</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14183,23 +14191,23 @@
         <v>112</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q101" s="2"/>
       <c r="R101" t="s" s="2">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="S101" t="s" s="2">
         <v>82</v>
@@ -14241,7 +14249,7 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -14262,21 +14270,21 @@
         <v>82</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>604</v>
+        <v>607</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14299,13 +14307,13 @@
         <v>82</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="N102" t="s" s="2">
         <v>377</v>
@@ -14358,7 +14366,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14379,7 +14387,7 @@
         <v>82</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="AN102" t="s" s="2">
         <v>414</v>
@@ -14390,10 +14398,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14416,13 +14424,13 @@
         <v>82</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -14473,7 +14481,7 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -14485,16 +14493,16 @@
         <v>82</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="AN103" t="s" s="2">
         <v>82</v>
@@ -14505,10 +14513,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14620,10 +14628,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14737,14 +14745,14 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
@@ -14766,10 +14774,10 @@
         <v>139</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="N106" t="s" s="2">
         <v>142</v>
@@ -14824,7 +14832,7 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -14856,10 +14864,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14885,13 +14893,13 @@
         <v>192</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
@@ -14921,25 +14929,25 @@
       </c>
       <c r="Y107" s="2"/>
       <c r="Z107" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="AA107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF107" t="s" s="2">
         <v>637</v>
-      </c>
-      <c r="AA107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF107" t="s" s="2">
-        <v>634</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>92</v>
@@ -14957,24 +14965,24 @@
         <v>82</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="AN107" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO107" t="s" s="2">
-        <v>639</v>
+        <v>642</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15000,13 +15008,13 @@
         <v>192</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -15035,10 +15043,10 @@
         <v>302</v>
       </c>
       <c r="Y108" t="s" s="2">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="Z108" t="s" s="2">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>82</v>
@@ -15056,7 +15064,7 @@
         <v>82</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15074,24 +15082,24 @@
         <v>82</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="AN108" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO108" t="s" s="2">
-        <v>648</v>
+        <v>651</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15114,13 +15122,13 @@
         <v>82</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="N109" t="s" s="2">
         <v>377</v>
@@ -15173,7 +15181,7 @@
         <v>82</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -15188,13 +15196,13 @@
         <v>104</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="AN109" t="s" s="2">
         <v>82</v>
@@ -15205,14 +15213,14 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
@@ -15231,16 +15239,16 @@
         <v>82</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -15290,7 +15298,7 @@
         <v>82</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -15311,7 +15319,7 @@
         <v>82</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="AN110" t="s" s="2">
         <v>82</v>
@@ -15322,10 +15330,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15348,16 +15356,16 @@
         <v>82</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
@@ -15407,7 +15415,7 @@
         <v>82</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -15422,13 +15430,13 @@
         <v>104</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="AL111" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="AN111" t="s" s="2">
         <v>82</v>

--- a/jpcore-r4b/develop/StructureDefinition-jp-medicationrequest.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-medicationrequest.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4140" uniqueCount="672">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4140" uniqueCount="674">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-dev</t>
+    <t>2.0.0-dev-temp</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-31</t>
+    <t>2025-07-30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>
@@ -377,7 +377,7 @@
     <t>IETF language tag</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.3.0</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -500,7 +500,15 @@
 このIDは業務手順によって定められた処方オーダに対して、直接的なURL参照が適切でない場合も含めて関連付けるために使われる。この業務手順のIDは実施者によって割り当てられたものであり、リソースが更新されたりサーバからサーバに転送されたとしても固定のものとして存続する。</t>
   </si>
   <si>
-    <t>これは業務IDであって、リソースに対するIDではない。</t>
+    <t xml:space="preserve">これは業務IDであって、リソースに対するIDではない。  
+Slice定義は下記のようになる。  
+[Sliceで定義される識別子]  
+　- rpNumber : 処方箋内部の剤グループとしてのRp番号  
+　- orderInRp : 同一RP番号（剤グループ）での薬剤の表記順  
+　- requestIdentifier : 処方オーダに対するID  
+　- prescriptionIdentifierCommon : 全国で⼀意になる発番ルールにもとづき発行される処方箋ID  
+[invariantで定義される識別子]  
+　- jp-inv-local-prescriptionid : 医療機関毎に管理される処方箋に対するID  </t>
   </si>
   <si>
     <t xml:space="preserve">value:system}
@@ -510,6 +518,10 @@
     <t>open</t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+jp-inv-local-prescriptionid:施設処方箋IDを記述する場合には、identifier.systemは、'urn:oid:1.2.392.100495.20.3.11.[1+施設番号10桁]'でなければならない。 {system.all(substring(0,31)!='urn:oid:1.2.392.100495.20.3.11.' or substring(31).matches('^1(0[1-9]|[1-3][0-9]|4[0-7])([0-9])([0-9]{7})$'))}</t>
+  </si>
+  <si>
     <t>Request.identifier</t>
   </si>
   <si>
@@ -632,7 +644,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.3.0</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -650,7 +662,7 @@
     <t>Rp番号(剤グループ番号)についてのsystem値</t>
   </si>
   <si>
-    <t>ここで付番されたIDがRp番号であることを明示するためにOIDとして定義された。urn:oid:1.2.392.100495.20.3.81で固定される。</t>
+    <t>ここで付番されたIDがRp番号であることを明示するためにOID-urlとして定義された。http://jpfhir.jp/fhir/core/mhlw/IdSystem/Medication-RPGroupNumberで固定される。</t>
   </si>
   <si>
     <t>Identifier.system is always case sensitive.</t>
@@ -659,7 +671,7 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>urn:oid:1.2.392.100495.20.3.81</t>
+    <t>http://jpfhir.jp/fhir/core/mhlw/IdSystem/Medication-RPGroupNumber</t>
   </si>
   <si>
     <t>http://www.acme.com/identifiers/patient</t>
@@ -736,7 +748,7 @@
     <t>MedicationRequest.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.3.0)
 </t>
   </si>
   <si>
@@ -791,10 +803,10 @@
     <t>RP番号内（剤グループ内）の連番を示すsystem値</t>
   </si>
   <si>
-    <t>剤グループ内番号の名前空間を識別するURI。固定値urn:oid:1.2.392.100495.20.3.82</t>
-  </si>
-  <si>
-    <t>urn:oid:1.2.392.100495.20.3.82</t>
+    <t>剤グループ内番号の名前空間を識別するURI。固定値 http://jpfhir.jp/fhir/core/mhlw/IdSystem/MedicationAdministrationIndex</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/mhlw/IdSystem/MedicationAdministrationIndex</t>
   </si>
   <si>
     <t>MedicationRequest.identifier:orderInRp.value</t>
@@ -812,34 +824,34 @@
     <t>MedicationRequest.identifier:orderInRp.assigner</t>
   </si>
   <si>
-    <t>MedicationRequest.identifier:requestIdentifierCommon</t>
-  </si>
-  <si>
-    <t>requestIdentifierCommon</t>
-  </si>
-  <si>
-    <t>処方箋に対するID</t>
-  </si>
-  <si>
-    <t>薬剤をオーダする単位としての処方箋に対するID。MedicationRequestは単一の薬剤でインスタンスが作成されるが、それの集合としての処方箋のID。system 要素には、保険医療機関番号を含む処方箋ID（urn:oid:1.2.392.100495.20.3.11.1[保険医療機関コード(10 桁)]）を指定する。全国で⼀意になる発番ルールにもとづく場合には urn:oid:1.2.392.100495.20.3.11 とする。</t>
+    <t>MedicationRequest.identifier:requestIdentifier</t>
+  </si>
+  <si>
+    <t>requestIdentifier</t>
+  </si>
+  <si>
+    <t>処方オーダに対するID</t>
+  </si>
+  <si>
+    <t>薬剤をオーダする単位としての処方依頼に対するID。MedicationRequestは単一の薬剤でインスタンスが作成される。</t>
   </si>
   <si>
     <t>This is a business identifier, not a resource identifier.</t>
   </si>
   <si>
-    <t>MedicationRequest.identifier:requestIdentifierCommon.id</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifierCommon.extension</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifierCommon.use</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifierCommon.type</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifierCommon.system</t>
+    <t>MedicationRequest.identifier:requestIdentifier.id</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:requestIdentifier.extension</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:requestIdentifier.use</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:requestIdentifier.type</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:requestIdentifier.system</t>
   </si>
   <si>
     <t>The namespace for the identifier value</t>
@@ -848,64 +860,64 @@
     <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
   </si>
   <si>
+    <t>http://jpfhir.jp/fhir/core/IdSystem/resourceInstance-identifier</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:requestIdentifier.value</t>
+  </si>
+  <si>
+    <t>The value that is unique</t>
+  </si>
+  <si>
+    <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
+  </si>
+  <si>
+    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4B/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:requestIdentifier.period</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:requestIdentifier.assigner</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:prescriptionIdentifierCommon</t>
+  </si>
+  <si>
+    <t>prescriptionIdentifierCommon</t>
+  </si>
+  <si>
+    <t>全国で⼀意となる処方箋ID</t>
+  </si>
+  <si>
+    <t>薬剤をオーダする単位としての処方箋に対するID。MedicationRequestは単一の薬剤でインスタンスが作成されるが、それの集合としての処方箋のID。全国で⼀意になる発番ルールにもとづき urn:oid:1.2.392.100495.20.3.11 とする。</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:prescriptionIdentifierCommon.id</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:prescriptionIdentifierCommon.extension</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:prescriptionIdentifierCommon.use</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:prescriptionIdentifierCommon.type</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:prescriptionIdentifierCommon.system</t>
+  </si>
+  <si>
     <t>urn:oid:1.2.392.100495.20.3.11</t>
   </si>
   <si>
-    <t>MedicationRequest.identifier:requestIdentifierCommon.value</t>
-  </si>
-  <si>
-    <t>The value that is unique</t>
-  </si>
-  <si>
-    <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
-  </si>
-  <si>
-    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4B/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifierCommon.period</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifierCommon.assigner</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifier</t>
-  </si>
-  <si>
-    <t>requestIdentifier</t>
-  </si>
-  <si>
-    <t>処方オーダに対するID</t>
-  </si>
-  <si>
-    <t>薬剤をオーダする単位としての処方依頼に対するID。MedicationRequestは単一の薬剤でインスタンスが作成される。</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifier.id</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifier.extension</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifier.use</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifier.type</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifier.system</t>
-  </si>
-  <si>
-    <t>http://jpfhir.jp/fhir/core/IdSystem/resourceInstance-identifier</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifier.value</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifier.period</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifier.assigner</t>
+    <t>MedicationRequest.identifier:prescriptionIdentifierCommon.value</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:prescriptionIdentifierCommon.period</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:prescriptionIdentifierCommon.assigner</t>
   </si>
   <si>
     <t>MedicationRequest.status</t>
@@ -953,7 +965,7 @@
     <t>Identifies the reasons for a given status.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medicationrequest-status-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/medicationrequest-status-reason|4.3.0</t>
   </si>
   <si>
     <t>Request.statusReason</t>
@@ -1068,8 +1080,8 @@
     <t>MedicationRequest.reported[x]</t>
   </si>
   <si>
-    <t>boolean
-Reference(Patient|Practitioner|PractitionerRole|RelatedPerson|Organization)</t>
+    <t xml:space="preserve">Reference(Patient|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|Practitioner|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|PractitionerRole|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|RelatedPerson|Organization|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization)
+</t>
   </si>
   <si>
     <t>初期記録にはない報告</t>
@@ -1093,7 +1105,7 @@
   <si>
     <t>If only a code is specified, then it needs to be a code for a specific product. If more information is required, then the use of the medication resource is recommended.  For example, if you require form or lot number, then you must reference the Medication resource.  
 ひとつのtext要素と、複数のcoding 要素を記述できる。処方オーダ時に選択または入力し、実際に処方箋に印字される文字列を必ずtext要素に格納した上で、それをコード化した情報を1個以上のcoding 要素に記述する。  
-厚生労働省標準であるHOT9コード（販社指定が不要な場合にはHOT7コード）または広く流通しているYJコードを用いるか、一般名処方の場合には厚生労働省保険局一般名処方マスタのコードを使用して、Coding要素（コードsystemを識別するURI、医薬品のコード、そのコード表における医薬品の名称の3つからなる）で記述する。  
+厚生労働省標準であるHOT9、HOT13コード（販社指定が不要な場合にはHOT7コード）または広く流通しているYJコードを用いるか、一般名処方の場合には厚生労働省保険局一般名処方マスタのコードを使用して、Coding要素（コードsystemを識別するURI、医薬品のコード、そのコード表における医薬品の名称の3つからなる）で記述する。  
 なお、上記のいずれの標準的コードも付番されていない医薬品や医療材料の場合には、薬機法の下で使用されているGS1標準の識別コードであるGTIN(Global Trade Item Number)の調剤包装単位（最少包装単位、個別包装単位）14桁を使用する。  
 ひとつの処方薬、医療材料を複数のコード体系のコードで記述してもよく、その場合にcoding 要素を繰り返して記述する。  
 ただし、ひとつの処方薬を複数のコードで繰り返し記述する場合には、それらのコードが指し示す処方薬、医療材料は当然同一でなければならない。  
@@ -1194,7 +1206,7 @@
     <t>MedicationRequest.supportingInformation</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.3.0)
 </t>
   </si>
   <si>
@@ -1220,7 +1232,7 @@
 </t>
   </si>
   <si>
-    <t>この処方オーダが最初に記述された日</t>
+    <t>この処方オーダが最初に記述された日時</t>
   </si>
   <si>
     <t>JP Coreでは必須。処方指示が最初に作成された日時。秒の精度まで記録する。タイムゾーンも付与しなければならない。</t>
@@ -1340,7 +1352,7 @@
     <t>A coded concept indicating why the medication was ordered.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-code</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-code|4.3.0</t>
   </si>
   <si>
     <t>Request.reasonCode</t>
@@ -1414,7 +1426,7 @@
     <t>MedicationRequest.basedOn</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|MedicationRequest|ServiceRequest|ImmunizationRecommendation)
+    <t xml:space="preserve">Reference(CarePlan|http://jpfhir.jp/fhir/core/StructureDefinition/JP_CarePlan|MedicationRequest|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRequest|ServiceRequest|http://jpfhir.jp/fhir/core/StructureDefinition/JP_ServiceRequest_Common|ImmunizationRecommendation)
 </t>
   </si>
   <si>
@@ -1463,7 +1475,7 @@
     <t>Identifies the overall pattern of medication administratio.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medicationrequest-course-of-therapy</t>
+    <t>http://hl7.org/fhir/ValueSet/medicationrequest-course-of-therapy|4.3.0</t>
   </si>
   <si>
     <t>Act.code where classCode = LIST and moodCode = EVN</t>
@@ -1495,7 +1507,7 @@
 </t>
   </si>
   <si>
-    <t>薬剤単位の備考</t>
+    <t>薬剤オーダごとの備考</t>
   </si>
   <si>
     <t>他の属性では伝えることができなかったMedicationRequestについての付加的情報。</t>
@@ -1805,12 +1817,15 @@
     <t>MedicationRequest.dispenseRequest.quantity</t>
   </si>
   <si>
-    <t>調剤量</t>
+    <t>払い出される薬剤量</t>
   </si>
   <si>
     <t>1回の調剤で払い出される薬剤の量</t>
   </si>
   <si>
+    <t>調剤後に払い出されるべき薬剤の量である。1日3錠、7日分という指示であれば21錠が払い出されるべき量である</t>
+  </si>
+  <si>
     <t>Message/Body/NewRx/MedicationPrescribed/DaysSupply</t>
   </si>
   <si>
@@ -1823,13 +1838,13 @@
     <t>MedicationRequest.dispenseRequest.expectedSupplyDuration</t>
   </si>
   <si>
-    <t>調剤日数</t>
-  </si>
-  <si>
-    <t>供給される製品が使用されるか、あるいは払い出しが想定されている時間を指定する期間。</t>
-  </si>
-  <si>
-    <t>状況によっては、この属性は物理的に供給される量というよりも、想定されている期間に供給される薬剤の量を指定する数量の代わりに使われることもある。たとえば、薬剤が90日間供給される（オーダされた量に基づいて）など。可能であれば、量も示した方がより正確になる。expectedSupplyDurationは外部要因に影響をうけることのある予測値である。</t>
+    <t>払い出される薬剤が想定された使用期間</t>
+  </si>
+  <si>
+    <t>払い出される薬剤が使用されることが想定された期間。</t>
+  </si>
+  <si>
+    <t>状況によっては、薬剤が供給される量として薬剤の錠数などの物理的量よりも、想定される供給期間を使って表現されることもある。たとえば、オーダされた量に基づいて薬剤を90日分提供するなど。可能であれば、量も示した方がより正確になる。ただし、実際には飲み忘れや紛失もあるためexpectedSupplyDurationは外部要因に影響をうけることのある予測値である。</t>
   </si>
   <si>
     <t>Message/Body/NewRx/MedicationPrescribed/Substitutions</t>
@@ -2061,7 +2076,7 @@
     <t>MedicationRequest.priorPrescription</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationRequest)
+    <t xml:space="preserve">Reference(MedicationRequest|4.3.0)
 </t>
   </si>
   <si>
@@ -2084,7 +2099,7 @@
 Drug Utilization Review (DUR)Alert</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DetectedIssue)
+    <t xml:space="preserve">Reference(DetectedIssue|4.3.0)
 </t>
   </si>
   <si>
@@ -2103,7 +2118,7 @@
     <t>MedicationRequest.eventHistory</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Provenance)
+    <t xml:space="preserve">Reference(Provenance|4.3.0)
 </t>
   </si>
   <si>
@@ -2426,17 +2441,17 @@
   <dimension ref="A1:AO111"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="69.44921875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="69.44921875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="24.5703125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="59.5390625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="59.5390625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="24.44140625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="244.94140625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2445,27 +2460,27 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="38.2265625" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="97.625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="75.55078125" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="59.37890625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="32.7734375" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="83.6953125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="64.76953125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="50.90625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="128.41796875" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="245.42578125" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="110.09375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3741,33 +3756,33 @@
         <v>82</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>104</v>
+        <v>158</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AO11" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B12" t="s" s="2">
         <v>150</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>82</v>
@@ -3792,13 +3807,13 @@
         <v>152</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -3863,27 +3878,27 @@
         <v>104</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AO12" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3909,10 +3924,10 @@
         <v>94</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -3963,7 +3978,7 @@
         <v>82</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -3984,7 +3999,7 @@
         <v>82</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>82</v>
@@ -3995,10 +4010,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -4027,7 +4042,7 @@
         <v>140</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N14" t="s" s="2">
         <v>142</v>
@@ -4068,10 +4083,10 @@
         <v>82</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AC14" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AD14" t="s" s="2">
         <v>82</v>
@@ -4080,7 +4095,7 @@
         <v>157</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
@@ -4101,7 +4116,7 @@
         <v>82</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>82</v>
@@ -4112,10 +4127,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -4141,16 +4156,16 @@
         <v>112</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>82</v>
@@ -4175,11 +4190,11 @@
         <v>82</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Y15" s="2"/>
       <c r="Z15" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>82</v>
@@ -4197,7 +4212,7 @@
         <v>82</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -4218,7 +4233,7 @@
         <v>82</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>82</v>
@@ -4229,10 +4244,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -4255,19 +4270,19 @@
         <v>93</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>82</v>
@@ -4292,11 +4307,11 @@
         <v>82</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Y16" s="2"/>
       <c r="Z16" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>82</v>
@@ -4314,7 +4329,7 @@
         <v>82</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -4335,21 +4350,21 @@
         <v>82</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4375,29 +4390,29 @@
         <v>106</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q17" s="2"/>
       <c r="R17" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="S17" t="s" s="2">
         <v>82</v>
       </c>
       <c r="T17" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="U17" t="s" s="2">
         <v>82</v>
@@ -4433,7 +4448,7 @@
         <v>82</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -4454,21 +4469,21 @@
         <v>82</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4491,16 +4506,16 @@
         <v>93</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -4514,7 +4529,7 @@
         <v>82</v>
       </c>
       <c r="T18" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="U18" t="s" s="2">
         <v>82</v>
@@ -4550,7 +4565,7 @@
         <v>82</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -4571,21 +4586,21 @@
         <v>82</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4608,13 +4623,13 @@
         <v>93</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4665,7 +4680,7 @@
         <v>82</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4686,21 +4701,21 @@
         <v>82</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4723,16 +4738,16 @@
         <v>93</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4782,7 +4797,7 @@
         <v>82</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4803,24 +4818,24 @@
         <v>82</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B21" t="s" s="2">
         <v>150</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>82</v>
@@ -4845,13 +4860,13 @@
         <v>152</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4916,27 +4931,27 @@
         <v>104</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4962,10 +4977,10 @@
         <v>94</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -5016,7 +5031,7 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -5037,7 +5052,7 @@
         <v>82</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>82</v>
@@ -5048,10 +5063,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5080,7 +5095,7 @@
         <v>140</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N23" t="s" s="2">
         <v>142</v>
@@ -5121,10 +5136,10 @@
         <v>82</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AD23" t="s" s="2">
         <v>82</v>
@@ -5133,7 +5148,7 @@
         <v>157</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -5154,7 +5169,7 @@
         <v>82</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>82</v>
@@ -5165,10 +5180,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5194,16 +5209,16 @@
         <v>112</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>82</v>
@@ -5228,11 +5243,11 @@
         <v>82</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Y24" s="2"/>
       <c r="Z24" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>82</v>
@@ -5250,7 +5265,7 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -5271,7 +5286,7 @@
         <v>82</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>82</v>
@@ -5282,10 +5297,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5308,19 +5323,19 @@
         <v>93</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>82</v>
@@ -5345,11 +5360,11 @@
         <v>82</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>82</v>
@@ -5367,7 +5382,7 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -5388,21 +5403,21 @@
         <v>82</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5428,29 +5443,29 @@
         <v>106</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="S26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="T26" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="U26" t="s" s="2">
         <v>82</v>
@@ -5486,7 +5501,7 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -5507,21 +5522,21 @@
         <v>82</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5544,16 +5559,16 @@
         <v>93</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5567,7 +5582,7 @@
         <v>82</v>
       </c>
       <c r="T27" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="U27" t="s" s="2">
         <v>82</v>
@@ -5603,7 +5618,7 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5624,21 +5639,21 @@
         <v>82</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5661,13 +5676,13 @@
         <v>93</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5718,7 +5733,7 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5739,21 +5754,21 @@
         <v>82</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5776,16 +5791,16 @@
         <v>93</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5835,7 +5850,7 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5856,24 +5871,24 @@
         <v>82</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B30" t="s" s="2">
         <v>150</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D30" t="s" s="2">
         <v>82</v>
@@ -5883,7 +5898,7 @@
         <v>80</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>82</v>
@@ -5898,13 +5913,13 @@
         <v>152</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5969,27 +5984,27 @@
         <v>104</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6015,10 +6030,10 @@
         <v>94</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -6069,7 +6084,7 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -6090,7 +6105,7 @@
         <v>82</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>82</v>
@@ -6101,10 +6116,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6133,7 +6148,7 @@
         <v>140</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N32" t="s" s="2">
         <v>142</v>
@@ -6174,10 +6189,10 @@
         <v>82</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>82</v>
@@ -6186,7 +6201,7 @@
         <v>157</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -6207,7 +6222,7 @@
         <v>82</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>82</v>
@@ -6218,10 +6233,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6247,16 +6262,16 @@
         <v>112</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>82</v>
@@ -6281,11 +6296,11 @@
         <v>82</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Y33" s="2"/>
       <c r="Z33" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>82</v>
@@ -6303,7 +6318,7 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -6324,7 +6339,7 @@
         <v>82</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>82</v>
@@ -6335,10 +6350,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6361,19 +6376,19 @@
         <v>93</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>82</v>
@@ -6398,11 +6413,11 @@
         <v>82</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Y34" s="2"/>
       <c r="Z34" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>82</v>
@@ -6420,7 +6435,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6441,21 +6456,21 @@
         <v>82</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6481,29 +6496,29 @@
         <v>106</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="S35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="T35" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="U35" t="s" s="2">
         <v>82</v>
@@ -6539,7 +6554,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6560,21 +6575,21 @@
         <v>82</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6597,16 +6612,16 @@
         <v>93</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6620,7 +6635,7 @@
         <v>82</v>
       </c>
       <c r="T36" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="U36" t="s" s="2">
         <v>82</v>
@@ -6656,7 +6671,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6677,21 +6692,21 @@
         <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6714,13 +6729,13 @@
         <v>93</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6771,7 +6786,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6792,21 +6807,21 @@
         <v>82</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6829,16 +6844,16 @@
         <v>93</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6888,7 +6903,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6909,24 +6924,24 @@
         <v>82</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B39" t="s" s="2">
         <v>150</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D39" t="s" s="2">
         <v>82</v>
@@ -6936,7 +6951,7 @@
         <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>82</v>
@@ -6951,13 +6966,13 @@
         <v>152</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -7022,27 +7037,27 @@
         <v>104</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7068,10 +7083,10 @@
         <v>94</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -7122,7 +7137,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -7143,7 +7158,7 @@
         <v>82</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>82</v>
@@ -7154,10 +7169,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7186,7 +7201,7 @@
         <v>140</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N41" t="s" s="2">
         <v>142</v>
@@ -7227,10 +7242,10 @@
         <v>82</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>82</v>
@@ -7239,7 +7254,7 @@
         <v>157</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -7260,7 +7275,7 @@
         <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>82</v>
@@ -7271,10 +7286,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7300,16 +7315,16 @@
         <v>112</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>82</v>
@@ -7334,11 +7349,11 @@
         <v>82</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Y42" s="2"/>
       <c r="Z42" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>82</v>
@@ -7356,7 +7371,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7377,7 +7392,7 @@
         <v>82</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>82</v>
@@ -7388,10 +7403,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7414,19 +7429,19 @@
         <v>93</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
@@ -7451,11 +7466,11 @@
         <v>82</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Y43" s="2"/>
       <c r="Z43" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>82</v>
@@ -7473,7 +7488,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7494,21 +7509,21 @@
         <v>82</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7534,29 +7549,29 @@
         <v>106</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q44" s="2"/>
       <c r="R44" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="S44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="T44" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="U44" t="s" s="2">
         <v>82</v>
@@ -7592,7 +7607,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7613,21 +7628,21 @@
         <v>82</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7650,16 +7665,16 @@
         <v>93</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7673,7 +7688,7 @@
         <v>82</v>
       </c>
       <c r="T45" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="U45" t="s" s="2">
         <v>82</v>
@@ -7709,7 +7724,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7730,21 +7745,21 @@
         <v>82</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7767,13 +7782,13 @@
         <v>93</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7824,7 +7839,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7845,21 +7860,21 @@
         <v>82</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7882,16 +7897,16 @@
         <v>93</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7941,7 +7956,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7962,21 +7977,21 @@
         <v>82</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8002,13 +8017,13 @@
         <v>112</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -8034,13 +8049,13 @@
         <v>82</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>82</v>
@@ -8058,7 +8073,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>92</v>
@@ -8073,16 +8088,16 @@
         <v>104</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>82</v>
@@ -8090,10 +8105,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8116,16 +8131,16 @@
         <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -8151,13 +8166,13 @@
         <v>82</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>82</v>
@@ -8175,7 +8190,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8190,13 +8205,13 @@
         <v>104</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>82</v>
@@ -8207,10 +8222,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8236,13 +8251,13 @@
         <v>112</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8268,13 +8283,13 @@
         <v>82</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>82</v>
@@ -8292,7 +8307,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>92</v>
@@ -8307,16 +8322,16 @@
         <v>104</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
@@ -8324,10 +8339,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8350,16 +8365,16 @@
         <v>82</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8389,7 +8404,7 @@
       </c>
       <c r="Y51" s="2"/>
       <c r="Z51" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>82</v>
@@ -8407,7 +8422,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8425,13 +8440,13 @@
         <v>82</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
@@ -8439,10 +8454,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8468,13 +8483,13 @@
         <v>112</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8500,13 +8515,13 @@
         <v>82</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>82</v>
@@ -8524,7 +8539,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8539,16 +8554,16 @@
         <v>104</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
@@ -8556,10 +8571,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8582,16 +8597,16 @@
         <v>93</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8641,7 +8656,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8662,7 +8677,7 @@
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>82</v>
@@ -8673,10 +8688,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8699,13 +8714,13 @@
         <v>93</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8756,7 +8771,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8777,7 +8792,7 @@
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>82</v>
@@ -8788,10 +8803,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8814,16 +8829,16 @@
         <v>93</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8852,10 +8867,10 @@
         <v>116</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>82</v>
@@ -8873,7 +8888,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>92</v>
@@ -8888,27 +8903,27 @@
         <v>104</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8931,16 +8946,16 @@
         <v>93</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8990,7 +9005,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>92</v>
@@ -9005,27 +9020,27 @@
         <v>104</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9048,16 +9063,16 @@
         <v>82</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9107,7 +9122,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9122,27 +9137,27 @@
         <v>104</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9165,16 +9180,16 @@
         <v>82</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9224,7 +9239,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9239,16 +9254,16 @@
         <v>104</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>82</v>
@@ -9256,10 +9271,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9282,13 +9297,13 @@
         <v>93</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9339,7 +9354,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9354,27 +9369,27 @@
         <v>104</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9397,16 +9412,16 @@
         <v>93</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9456,7 +9471,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9471,16 +9486,16 @@
         <v>104</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>82</v>
@@ -9488,10 +9503,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9514,16 +9529,16 @@
         <v>82</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9573,7 +9588,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9588,16 +9603,16 @@
         <v>104</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
@@ -9605,10 +9620,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9631,16 +9646,16 @@
         <v>93</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9666,11 +9681,11 @@
         <v>82</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Y62" s="2"/>
       <c r="Z62" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>82</v>
@@ -9688,7 +9703,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9703,13 +9718,13 @@
         <v>104</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>82</v>
@@ -9720,10 +9735,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9746,16 +9761,16 @@
         <v>82</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9805,7 +9820,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9826,10 +9841,10 @@
         <v>82</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>
@@ -9837,10 +9852,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9863,16 +9878,16 @@
         <v>82</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9898,13 +9913,13 @@
         <v>82</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>82</v>
@@ -9922,7 +9937,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9937,27 +9952,27 @@
         <v>104</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9980,16 +9995,16 @@
         <v>82</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -10039,7 +10054,7 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -10054,16 +10069,16 @@
         <v>104</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>82</v>
@@ -10071,10 +10086,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10097,16 +10112,16 @@
         <v>93</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -10156,7 +10171,7 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10171,13 +10186,13 @@
         <v>104</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>82</v>
@@ -10188,10 +10203,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10217,13 +10232,13 @@
         <v>106</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -10273,7 +10288,7 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10294,7 +10309,7 @@
         <v>82</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>82</v>
@@ -10305,10 +10320,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10331,16 +10346,16 @@
         <v>93</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10390,7 +10405,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10405,13 +10420,13 @@
         <v>104</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>82</v>
@@ -10422,10 +10437,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10451,14 +10466,14 @@
         <v>152</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>82</v>
@@ -10507,7 +10522,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10522,13 +10537,13 @@
         <v>104</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>82</v>
@@ -10539,10 +10554,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10565,16 +10580,16 @@
         <v>82</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10600,13 +10615,13 @@
         <v>82</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>82</v>
@@ -10624,7 +10639,7 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10645,7 +10660,7 @@
         <v>82</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>82</v>
@@ -10656,10 +10671,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10682,16 +10697,16 @@
         <v>82</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10741,7 +10756,7 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10756,13 +10771,13 @@
         <v>104</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>82</v>
@@ -10773,10 +10788,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10799,16 +10814,16 @@
         <v>82</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10858,7 +10873,7 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10873,13 +10888,13 @@
         <v>104</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>82</v>
@@ -10890,10 +10905,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10916,16 +10931,16 @@
         <v>82</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10975,7 +10990,7 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -10990,13 +11005,13 @@
         <v>104</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AL73" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>82</v>
@@ -11007,10 +11022,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11033,13 +11048,13 @@
         <v>82</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -11090,7 +11105,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11102,16 +11117,16 @@
         <v>82</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>82</v>
@@ -11122,10 +11137,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11148,13 +11163,13 @@
         <v>82</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -11205,7 +11220,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11226,7 +11241,7 @@
         <v>82</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>82</v>
@@ -11237,10 +11252,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11266,10 +11281,10 @@
         <v>139</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -11308,7 +11323,7 @@
         <v>82</v>
       </c>
       <c r="AB76" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AC76" s="2"/>
       <c r="AD76" t="s" s="2">
@@ -11318,7 +11333,7 @@
         <v>157</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11350,13 +11365,13 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C77" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D77" t="s" s="2">
         <v>82</v>
@@ -11378,13 +11393,13 @@
         <v>82</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11435,7 +11450,7 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11444,10 +11459,10 @@
         <v>81</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>82</v>
@@ -11467,13 +11482,13 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="D78" t="s" s="2">
         <v>82</v>
@@ -11495,13 +11510,13 @@
         <v>82</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11552,7 +11567,7 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11561,10 +11576,10 @@
         <v>81</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>82</v>
@@ -11584,14 +11599,14 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
@@ -11613,10 +11628,10 @@
         <v>139</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="N79" t="s" s="2">
         <v>142</v>
@@ -11671,7 +11686,7 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -11703,10 +11718,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11729,16 +11744,16 @@
         <v>82</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -11788,7 +11803,7 @@
         <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -11800,7 +11815,7 @@
         <v>82</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>82</v>
@@ -11809,7 +11824,7 @@
         <v>82</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>82</v>
@@ -11820,10 +11835,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11846,13 +11861,13 @@
         <v>82</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -11903,7 +11918,7 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -11924,7 +11939,7 @@
         <v>82</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>82</v>
@@ -11935,10 +11950,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11967,7 +11982,7 @@
         <v>140</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N82" t="s" s="2">
         <v>142</v>
@@ -12020,7 +12035,7 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -12041,7 +12056,7 @@
         <v>82</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>82</v>
@@ -12052,14 +12067,14 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
@@ -12081,10 +12096,10 @@
         <v>139</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="N83" t="s" s="2">
         <v>142</v>
@@ -12139,7 +12154,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12171,10 +12186,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12197,16 +12212,16 @@
         <v>82</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12256,7 +12271,7 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12277,7 +12292,7 @@
         <v>82</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>82</v>
@@ -12288,10 +12303,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12314,16 +12329,16 @@
         <v>82</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12373,7 +12388,7 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12394,7 +12409,7 @@
         <v>82</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>82</v>
@@ -12405,10 +12420,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12431,16 +12446,16 @@
         <v>82</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -12490,7 +12505,7 @@
         <v>82</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12511,7 +12526,7 @@
         <v>82</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>82</v>
@@ -12522,10 +12537,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12548,19 +12563,19 @@
         <v>82</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>82</v>
@@ -12609,7 +12624,7 @@
         <v>82</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -12627,10 +12642,10 @@
         <v>82</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>82</v>
@@ -12641,10 +12656,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12670,10 +12685,10 @@
         <v>94</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -12724,7 +12739,7 @@
         <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -12745,7 +12760,7 @@
         <v>82</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>82</v>
@@ -12756,10 +12771,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12788,7 +12803,7 @@
         <v>140</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N89" t="s" s="2">
         <v>142</v>
@@ -12829,10 +12844,10 @@
         <v>82</v>
       </c>
       <c r="AB89" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AC89" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AD89" t="s" s="2">
         <v>82</v>
@@ -12841,7 +12856,7 @@
         <v>157</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -12862,7 +12877,7 @@
         <v>82</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>82</v>
@@ -12873,10 +12888,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12899,16 +12914,16 @@
         <v>93</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -12958,7 +12973,7 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -12967,7 +12982,7 @@
         <v>92</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AJ90" t="s" s="2">
         <v>104</v>
@@ -12979,21 +12994,21 @@
         <v>82</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13016,23 +13031,23 @@
         <v>93</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q91" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="R91" t="s" s="2">
         <v>82</v>
@@ -13077,7 +13092,7 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13086,7 +13101,7 @@
         <v>92</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AJ91" t="s" s="2">
         <v>104</v>
@@ -13098,21 +13113,21 @@
         <v>82</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13135,16 +13150,16 @@
         <v>82</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -13194,7 +13209,7 @@
         <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13212,24 +13227,24 @@
         <v>82</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13252,16 +13267,16 @@
         <v>82</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>525</v>
+        <v>572</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -13311,7 +13326,7 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13329,24 +13344,24 @@
         <v>82</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="AN93" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13369,16 +13384,16 @@
         <v>82</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -13428,7 +13443,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13446,10 +13461,10 @@
         <v>82</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>82</v>
@@ -13460,10 +13475,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13489,10 +13504,10 @@
         <v>94</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -13543,7 +13558,7 @@
         <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -13564,7 +13579,7 @@
         <v>82</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AN95" t="s" s="2">
         <v>82</v>
@@ -13575,10 +13590,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13607,7 +13622,7 @@
         <v>140</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N96" t="s" s="2">
         <v>142</v>
@@ -13648,10 +13663,10 @@
         <v>82</v>
       </c>
       <c r="AB96" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AC96" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AD96" t="s" s="2">
         <v>82</v>
@@ -13660,7 +13675,7 @@
         <v>157</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -13681,7 +13696,7 @@
         <v>82</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AN96" t="s" s="2">
         <v>82</v>
@@ -13692,10 +13707,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13718,19 +13733,19 @@
         <v>93</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>82</v>
@@ -13779,7 +13794,7 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -13800,21 +13815,21 @@
         <v>82</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="AN97" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13840,20 +13855,20 @@
         <v>112</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q98" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="R98" t="s" s="2">
         <v>82</v>
@@ -13874,11 +13889,11 @@
         <v>82</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Y98" s="2"/>
       <c r="Z98" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>82</v>
@@ -13896,7 +13911,7 @@
         <v>82</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -13917,21 +13932,21 @@
         <v>82</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="AN98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13954,24 +13969,24 @@
         <v>93</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q99" s="2"/>
       <c r="R99" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="S99" t="s" s="2">
         <v>82</v>
@@ -14013,7 +14028,7 @@
         <v>82</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -14034,21 +14049,21 @@
         <v>82</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="AN99" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO99" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14074,21 +14089,21 @@
         <v>106</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q100" s="2"/>
       <c r="R100" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="S100" t="s" s="2">
         <v>82</v>
@@ -14130,7 +14145,7 @@
         <v>82</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14139,7 +14154,7 @@
         <v>92</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="AJ100" t="s" s="2">
         <v>104</v>
@@ -14151,21 +14166,21 @@
         <v>82</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14191,23 +14206,23 @@
         <v>112</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q101" s="2"/>
       <c r="R101" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="S101" t="s" s="2">
         <v>82</v>
@@ -14249,7 +14264,7 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -14270,21 +14285,21 @@
         <v>82</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14307,16 +14322,16 @@
         <v>82</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -14366,7 +14381,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14387,10 +14402,10 @@
         <v>82</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>82</v>
@@ -14398,10 +14413,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14424,13 +14439,13 @@
         <v>82</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -14481,7 +14496,7 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -14493,16 +14508,16 @@
         <v>82</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="AN103" t="s" s="2">
         <v>82</v>
@@ -14513,10 +14528,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14539,13 +14554,13 @@
         <v>82</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -14596,7 +14611,7 @@
         <v>82</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -14617,7 +14632,7 @@
         <v>82</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AN104" t="s" s="2">
         <v>82</v>
@@ -14628,10 +14643,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14660,7 +14675,7 @@
         <v>140</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N105" t="s" s="2">
         <v>142</v>
@@ -14713,7 +14728,7 @@
         <v>82</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -14734,7 +14749,7 @@
         <v>82</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AN105" t="s" s="2">
         <v>82</v>
@@ -14745,14 +14760,14 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
@@ -14774,10 +14789,10 @@
         <v>139</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="N106" t="s" s="2">
         <v>142</v>
@@ -14832,7 +14847,7 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -14864,10 +14879,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14890,16 +14905,16 @@
         <v>82</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
@@ -14929,7 +14944,7 @@
       </c>
       <c r="Y107" s="2"/>
       <c r="Z107" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>82</v>
@@ -14947,7 +14962,7 @@
         <v>82</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>92</v>
@@ -14965,24 +14980,24 @@
         <v>82</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="AN107" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO107" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15005,16 +15020,16 @@
         <v>82</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -15040,13 +15055,13 @@
         <v>82</v>
       </c>
       <c r="X108" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Y108" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="Z108" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>82</v>
@@ -15064,7 +15079,7 @@
         <v>82</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15082,24 +15097,24 @@
         <v>82</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="AN108" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO108" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15122,16 +15137,16 @@
         <v>82</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
@@ -15181,7 +15196,7 @@
         <v>82</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -15196,13 +15211,13 @@
         <v>104</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="AN109" t="s" s="2">
         <v>82</v>
@@ -15213,14 +15228,14 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
@@ -15239,16 +15254,16 @@
         <v>82</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -15298,7 +15313,7 @@
         <v>82</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -15319,7 +15334,7 @@
         <v>82</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="AN110" t="s" s="2">
         <v>82</v>
@@ -15330,10 +15345,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15356,16 +15371,16 @@
         <v>82</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
@@ -15415,7 +15430,7 @@
         <v>82</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -15430,13 +15445,13 @@
         <v>104</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="AL111" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="AN111" t="s" s="2">
         <v>82</v>

--- a/jpcore-r4b/develop/StructureDefinition-jp-medicationrequest.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-medicationrequest.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-dev-temp</t>
+    <t>2.0.0-dev</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4b/develop/StructureDefinition-jp-medicationrequest.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-medicationrequest.xlsx
@@ -275,8 +275,8 @@
     <t>患者への薬の供給と内服・外用薬剤処方の指示を共に提供するオーダ。ケアプランやワークフローパターンとハーモナイズし、入院や外来でも使えるようにするため、このリソースは"MedicationPrescription"や"MedicationOrder"ではなく、"MedicationRequest"と呼ばれる。MedicationRequestプロファイルからの派生プロファイルである。</t>
   </si>
   <si>
-    <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where(((id.exists() and ('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url)))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(uri) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
+    <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where(((id.exists() and ('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url)))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(uri) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が存在することが望ましい / A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Request</t>
@@ -304,13 +304,13 @@
 </t>
   </si>
   <si>
-    <t>Logical id of this artifact</t>
-  </si>
-  <si>
-    <t>The logical id of the resource, as used in the URL for the resource. Once assigned, this value never changes.</t>
-  </si>
-  <si>
-    <t>The only time that a resource does not have an id is when it is being submitted to the server using a create operation.</t>
+    <t>このアーティファクトの論理ID / Logical id of this artifact</t>
+  </si>
+  <si>
+    <t>リソースのURLで使用されるリソースの論理ID。割り当てられたら、この値は変更されません。 / The logical id of the resource, as used in the URL for the resource. Once assigned, this value never changes.</t>
+  </si>
+  <si>
+    <t>リソースにIDがないのは、IDが作成操作を使用してサーバーに送信されている場合です。 / The only time that a resource does not have an id is when it is being submitted to the server using a create operation.</t>
   </si>
   <si>
     <t>Resource.id</t>
@@ -323,16 +323,16 @@
 </t>
   </si>
   <si>
-    <t>Metadata about the resource</t>
-  </si>
-  <si>
-    <t>The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
+    <t>リソースに関するMetadata / Metadata about the resource</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
   </si>
   <si>
     <t>Resource.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -343,13 +343,13 @@
 </t>
   </si>
   <si>
-    <t>A set of rules under which this content was created</t>
-  </si>
-  <si>
-    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
-  </si>
-  <si>
-    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
+    <t>このコンテンツが作成されたルールのセット / A set of rules under which this content was created</t>
+  </si>
+  <si>
+    <t>リソースが構築されたときに従った一連のルールへの参照。コンテンツの処理時に理解する必要があります。多くの場合、これは他のプロファイルなどとともに特別なルールを定義する実装ガイドへの参照です。 / A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
+  </si>
+  <si>
+    <t>このルールセットを主張することは、コンテンツが限られた取引パートナーのセットによってのみ理解されることを制限します。これにより、本質的に長期的にデータの有用性が制限されます。ただし、既存の健康エコシステムは非常に破壊されており、一般的に計算可能な意味でデータを定義、収集、交換する準備ができていません。可能な限り、実装者や仕様ライターはこの要素の使用を避ける必要があります。多くの場合、使用する場合、URLは、これらの特別なルールを他のプロファイル、バリューセットなどとともに叙述(Narative)の一部として定義する実装ガイドへの参照です。 / Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
   </si>
   <si>
     <t>Resource.implicitRules</t>
@@ -362,19 +362,19 @@
 </t>
   </si>
   <si>
-    <t>Language of the resource content</t>
-  </si>
-  <si>
-    <t>The base language in which the resource is written.</t>
-  </si>
-  <si>
-    <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
+    <t>リソースコンテンツの言語 / Language of the resource content</t>
+  </si>
+  <si>
+    <t>リソースが書かれている基本言語。 / The base language in which the resource is written.</t>
+  </si>
+  <si>
+    <t>言語は、インデックス作成とアクセシビリティをサポートするために提供されます（通常、テキストから音声までのサービスなどのサービスが言語タグを使用します）。叙述(Narative)のHTML言語タグは、叙述(Narative)に適用されます。リソース上の言語タグを使用して、リソース内のデータから生成された他のプレゼンテーションの言語を指定できます。すべてのコンテンツが基本言語である必要はありません。リソース。言語は、叙述(Narative)に自動的に適用されると想定されるべきではありません。言語が指定されている場合、HTMLのDIV要素にも指定されている場合（XML：LangとHTML Lang属性の関係については、HTML5のルールを参照してください）。 / Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
   </si>
   <si>
     <t>preferred</t>
   </si>
   <si>
-    <t>IETF language tag</t>
+    <t>IETF言語タグ / IETF language tag</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages|4.3.0</t>
@@ -394,13 +394,13 @@
 </t>
   </si>
   <si>
-    <t>Text summary of the resource, for human interpretation</t>
-  </si>
-  <si>
-    <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
-  </si>
-  <si>
-    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
+    <t>人間の解釈のためのリソースのテキスト概要 / Text summary of the resource, for human interpretation</t>
+  </si>
+  <si>
+    <t>リソースの概要を含み、人間へのリソースの内容を表すために使用できる人間の読み取り可能な叙述(Narative)。叙述(Narative)はすべての構造化されたデータをエンコードする必要はありませんが、人間が叙述(Narative)を読むだけで「臨床的に安全」にするために十分な詳細を含める必要があります。リソースの定義は、臨床的安全を確保するために、叙述(Narative)で表現するコンテンツを定義する場合があります。 / A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
+  </si>
+  <si>
+    <t>含まれるリソースには叙述(Narative)がありません。含まれていないリソースには叙述(Narative)が必要です。場合によっては、リソースには、追加の個別のデータがほとんどまたはまったくないテキストのみがあります（すべてのMinoccur = 1要素が満たされている限り）。これは、情報がtext blob (バイナリー ラージ オブジェクト)としてキャプチャされるレガシーシステムからのデータ、またはテキストが生またはナレーションされ、エンコードされた情報が後で追加される場合に必要になる場合があります。 / Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
   </si>
   <si>
     <t>DomainResource.text</t>
@@ -420,19 +420,19 @@
 </t>
   </si>
   <si>
-    <t>Contained, inline Resources</t>
-  </si>
-  <si>
-    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
-  </si>
-  <si>
-    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
+    <t>インラインリソースが含まれています / Contained, inline Resources</t>
+  </si>
+  <si>
+    <t>これらのリソースには、それらを含むリソースを除いて独立した存在はありません - 独立して特定することはできず、独自の独立したトランザクションスコープを持つこともできません。 / These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
+  </si>
+  <si>
+    <t>識別が失われると、コンテンツを適切に識別できる場合は、これを行うべきではありません。含まれるリソースには、メタ要素にプロファイルとタグがある場合がありますが、セキュリティラベルはありません。 / This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
   </si>
   <si>
     <t>DomainResource.contained</t>
   </si>
   <si>
-    <t xml:space="preserve">dom-r4b:Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
+    <t xml:space="preserve">dom-r4b:R4リソース内に新しいR4Bリソースを含めると、インスタンスがR4システムと共有された場合に相互運用性の問題が発生する可能性があります / Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
 </t>
   </si>
   <si>
@@ -450,33 +450,34 @@
 </t>
   </si>
   <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+    <t>実装で定義された追加のコンテンツ / Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>リソースの基本的な定義の一部ではない追加情報を表すために使用できます。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。 / May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>拡張機能を使用または定義する機関や管轄権に関係なく、アプリケーション、プロジェクト、または標準による拡張機能の使用に関連するスティグマはありません。拡張機能の使用は、FHIR仕様がすべての人にコアレベルのシンプルさを保持できるようにするものです。 / There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
     <t>DomainResource.extension</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>MedicationRequest.modifierExtension</t>
   </si>
   <si>
-    <t>Extensions that cannot be ignored</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+    <t>無視できない拡張機能 / Extensions that cannot be ignored</t>
+  </si>
+  <si>
+    <t>リソースの基本的な定義の一部ではなく、それを含む要素の理解および/または含有要素の子孫の理解を変更するために使用される場合があります。通常、修飾子要素は否定または資格を提供します。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義することが許可されていますが、拡張機能の定義の一部として満たされる一連の要件があります。アプリケーションの処理リソースは、修飾子拡張機能をチェックする必要があります。
+モディファイア拡張は、リソースまたはdomainResource上の要素の意味を変更してはなりません（修飾軸自体の意味を変更することはできません）。 / May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
+    <t>修飾子拡張機能により、安全に無視できる大部分の拡張機能と明確に区別できるように、安全に無視できない拡張機能が可能になります。これにより、実装者が拡張の存在を禁止する必要性を排除することにより、相互運用性が促進されます。詳細については、[修飾子拡張の定義]（拡張性.html＃modifierextension）を参照してください。 / Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -518,7 +519,7 @@
     <t>open</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 jp-inv-local-prescriptionid:施設処方箋IDを記述する場合には、identifier.systemは、'urn:oid:1.2.392.100495.20.3.11.[1+施設番号10桁]'でなければならない。 {system.all(substring(0,31)!='urn:oid:1.2.392.100495.20.3.11.' or substring(31).matches('^1(0[1-9]|[1-3][0-9]|4[0-7])([0-9])([0-9]{7})$'))}</t>
   </si>
   <si>
@@ -558,10 +559,10 @@
     <t>MedicationRequest.identifier.id</t>
   </si>
   <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+    <t>要素間参照のための一意のID / Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>リソース内の要素の一意のID（内部参照用）。これは、スペースを含まない文字列値である場合があります。 / Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
   </si>
   <si>
     <t>Element.id</t>
@@ -576,7 +577,7 @@
     <t>MedicationRequest.identifier.extension</t>
   </si>
   <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+    <t>要素の基本的な定義の一部ではない追加情報を表すために使用できます。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。 / May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
     <t xml:space="preserve">value:url}
@@ -595,16 +596,16 @@
     <t>MedicationRequest.identifier.use</t>
   </si>
   <si>
-    <t>usual | official | temp | secondary | old (If known)</t>
-  </si>
-  <si>
-    <t>The purpose of this identifier.</t>
-  </si>
-  <si>
-    <t>Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
-  </si>
-  <si>
-    <t>Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
+    <t>通常|公式|一時的|セカンダリ|古い（知られている場合） / usual | official | temp | secondary | old (If known)</t>
+  </si>
+  <si>
+    <t>このidentifierの目的。 / The purpose of this identifier.</t>
+  </si>
+  <si>
+    <t>アプリケーションは、identifierが一時的なものであると明示的に言っていない限り、永続的であると想定できます。 / Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
+  </si>
+  <si>
+    <t>特定の使用のコンテキストが一連のidentifierの中から選択される適切なidentifierを許可します。 / Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
   </si>
   <si>
     <t>required</t>
@@ -629,16 +630,16 @@
 </t>
   </si>
   <si>
-    <t>Description of identifier</t>
-  </si>
-  <si>
-    <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
-  </si>
-  <si>
-    <t>Allows users to make use of identifiers when the identifier system is not known.</t>
+    <t>identifierの説明 / Description of identifier</t>
+  </si>
+  <si>
+    <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>この要素は、identifierの一般的なカテゴリのみを扱います。identifier。システムに対応するコードに使用しないでください。一部のidentifierは、一般的な使用法により複数のカテゴリに分類される場合があります。システムがわかっている場合、タイプは常にシステム定義の一部であるため、タイプは不要です。ただし、システムが不明なidentifierを処理する必要があることがよくあります。多くの異なるシステムが同じタイプを持っているため、タイプとシステムの間に1：1の関係はありません。 / This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
+  </si>
+  <si>
+    <t>identifierシステムが不明な場合、ユーザーはidentifierを使用できます。 / Allows users to make use of identifiers when the identifier system is not known.</t>
   </si>
   <si>
     <t>extensible</t>
@@ -665,10 +666,10 @@
     <t>ここで付番されたIDがRp番号であることを明示するためにOID-urlとして定義された。http://jpfhir.jp/fhir/core/mhlw/IdSystem/Medication-RPGroupNumberで固定される。</t>
   </si>
   <si>
-    <t>Identifier.system is always case sensitive.</t>
-  </si>
-  <si>
-    <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
+    <t>identifier。システムは常にケースに敏感です。 / Identifier.system is always case sensitive.</t>
+  </si>
+  <si>
+    <t>identifierのセットがたくさんあります。2つのidentifierを一致させるには、どのセットを扱っているかを知る必要があります。システムは、特定の一意のidentifierセットを識別します。 / There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
     <t>http://jpfhir.jp/fhir/core/mhlw/IdSystem/Medication-RPGroupNumber</t>
@@ -727,10 +728,10 @@
 </t>
   </si>
   <si>
-    <t>Time period when id is/was valid for use</t>
-  </si>
-  <si>
-    <t>Time period during which identifier is/was valid for use.</t>
+    <t>IDが使用に有効だった時間期間 / Time period when id is/was valid for use</t>
+  </si>
+  <si>
+    <t>identifierが使用される/有効な期間。 / Time period during which identifier is/was valid for use.</t>
   </si>
   <si>
     <t>Identifier.period</t>
@@ -752,13 +753,13 @@
 </t>
   </si>
   <si>
-    <t>Organization that issued id (may be just text)</t>
-  </si>
-  <si>
-    <t>Organization that issued/manages the identifier.</t>
-  </si>
-  <si>
-    <t>The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
+    <t>IDを発行した組織（単なるテキストである可能性があります） / Organization that issued id (may be just text)</t>
+  </si>
+  <si>
+    <t>identifierを発行/管理する組織。 / Organization that issued/manages the identifier.</t>
+  </si>
+  <si>
+    <t>identifierは、.reference要素を省略し、割り当て組織に関する名前またはその他のテキスト情報を反映した.display要素のみを含む場合があります。 / The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
   </si>
   <si>
     <t>Identifier.assigner</t>
@@ -836,7 +837,7 @@
     <t>薬剤をオーダする単位としての処方依頼に対するID。MedicationRequestは単一の薬剤でインスタンスが作成される。</t>
   </si>
   <si>
-    <t>This is a business identifier, not a resource identifier.</t>
+    <t>これはビジネスidentifierであり、リソースidentifierではありません。 / This is a business identifier, not a resource identifier.</t>
   </si>
   <si>
     <t>MedicationRequest.identifier:requestIdentifier.id</t>
@@ -854,10 +855,10 @@
     <t>MedicationRequest.identifier:requestIdentifier.system</t>
   </si>
   <si>
-    <t>The namespace for the identifier value</t>
-  </si>
-  <si>
-    <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
+    <t>identifier値の名前空間 / The namespace for the identifier value</t>
+  </si>
+  <si>
+    <t>値の名前空間、つまり一意のセット値を記述するURLを確立します。 / Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
   </si>
   <si>
     <t>http://jpfhir.jp/fhir/core/IdSystem/resourceInstance-identifier</t>
@@ -866,13 +867,13 @@
     <t>MedicationRequest.identifier:requestIdentifier.value</t>
   </si>
   <si>
-    <t>The value that is unique</t>
-  </si>
-  <si>
-    <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
-  </si>
-  <si>
-    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4B/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+    <t>一意の値 / The value that is unique</t>
+  </si>
+  <si>
+    <t>通常、identifierの部分はユーザーに関連し、システムのコンテキスト内で一意のユーザーに関連しています。 / The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
+  </si>
+  <si>
+    <t>値が完全なURIの場合、システムはurn：ietf：rfc：3986でなければなりません。値の主な目的は、計算マッピングです。その結果、比較目的で正規化される可能性があります（例えば、有意でない白文字、ダッシュなどの削除）ヒューマンディスプレイ用の値は、[レンダリングされた値拡張]（拡張レンダリングValue.html）を使用して伝達できます。identifier。価値は、identifierの知識を使用しない限り、ケースに敏感なものとして扱われます。システムにより、プロセッサーは、非セイズに固有の処理が安全であると確信できます。 / If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4B/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
   </si>
   <si>
     <t>MedicationRequest.identifier:requestIdentifier.period</t>
@@ -932,7 +933,7 @@
     <t>このエレメントはmodifierとされている。StatusとはこのResourceが現在妥当な状態ではないことも示すからである。</t>
   </si>
   <si>
-    <t>A coded concept specifying the state of the prescribing event. Describes the lifecycle of the prescription.</t>
+    <t>処方イベントの状態を指定するコード化された概念。処方箋のライフサイクルについて説明します。 / A coded concept specifying the state of the prescribing event. Describes the lifecycle of the prescription.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/medicationrequest-status|4.3.0</t>
@@ -962,7 +963,7 @@
     <t>example</t>
   </si>
   <si>
-    <t>Identifies the reasons for a given status.</t>
+    <t>特定のステータスの理由を特定します。 / Identifies the reasons for a given status.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/medicationrequest-status-reason|4.3.0</t>
@@ -988,7 +989,7 @@
 intentはこのresourceが実際に適応される時に変化するため、このエレメントはmodifierとしてラベルされる。</t>
   </si>
   <si>
-    <t>The kind of medication order.</t>
+    <t>種類の薬順。 / The kind of medication order.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/medicationrequest-intent|4.3.0</t>
@@ -1043,7 +1044,7 @@
     <t>FHIRでは文字列の大きさが1MBを超えてはならない(SHALL NOT)。</t>
   </si>
   <si>
-    <t>Identifies the level of importance to be assigned to actioning the request.</t>
+    <t>リクエストの実行に割り当てられる重要性のレベルを特定します。 / Identifies the level of importance to be assigned to actioning the request.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/request-priority|4.3.0</t>
@@ -1349,7 +1350,7 @@
     <t>このエレメントは病名コードであってもよい。もし、すべての条件を示す記録があって他の詳細な記録が必要であれば、reasonReferenceを使用すること。</t>
   </si>
   <si>
-    <t>A coded concept indicating why the medication was ordered.</t>
+    <t>薬が注文された理由を示すコード化された概念。 / A coded concept indicating why the medication was ordered.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/condition-code|4.3.0</t>
@@ -1472,7 +1473,7 @@
     <t>この属性は薬剤プロトコールと混同してはならない。</t>
   </si>
   <si>
-    <t>Identifies the overall pattern of medication administratio.</t>
+    <t>投薬投与の全体的なパターンを特定します。 / Identifies the overall pattern of medication administratio.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/medicationrequest-course-of-therapy|4.3.0</t>
@@ -1532,13 +1533,13 @@
 </t>
   </si>
   <si>
-    <t>How the medication should be taken</t>
-  </si>
-  <si>
-    <t>Indicates how the medication is to be used by the patient.</t>
-  </si>
-  <si>
-    <t>There are examples where a medication request may include the option of an oral dose or an Intravenous or Intramuscular dose.  For example, "Ondansetron 8mg orally or IV twice a day as needed for nausea" or "Compazine® (prochlorperazine) 5-10mg PO or 25mg PR bid prn nausea or vomiting".  In these cases, two medication requests would be created that could be grouped together.  The decision on which dose and route of administration to use is based on the patient's condition at the time the dose is needed.</t>
+    <t>薬をどのように服用すべきか / How the medication should be taken</t>
+  </si>
+  <si>
+    <t>患者が薬をどのように使用するかを示します。 / Indicates how the medication is to be used by the patient.</t>
+  </si>
+  <si>
+    <t>薬の要求には、経口投与または静脈内または筋肉内の用量のオプションが含まれる場合があります。たとえば、「吐き気に必要に応じて、1日に2回Ondansetron 8mgまたはIV」または「Compazine®（プロクロロペラジン）5-10mg POまたは25mg PR BID PRN吐き気または嘔吐」。これらの場合、グループ化できる2つの投薬要求が作成されます。使用する投与経路の決定は、用量が必要な時点での患者の状態に基づいています。 / There are examples where a medication request may include the option of an oral dose or an Intravenous or Intramuscular dose.  For example, "Ondansetron 8mg orally or IV twice a day as needed for nausea" or "Compazine® (prochlorperazine) 5-10mg PO or 25mg PR bid prn nausea or vomiting".  In these cases, two medication requests would be created that could be grouped together.  The decision on which dose and route of administration to use is based on the patient's condition at the time the dose is needed.</t>
   </si>
   <si>
     <t>Request.occurrence[x]</t>
@@ -1560,7 +1561,7 @@
     <t>薬剤オーダ(MedicationRequest, Medication Prescription, Medication Orderなどとしても表現される）や薬剤オーダとの一部としての薬剤の払い出しあるいは提供。この情報はオーダとしてかならず伝えられるというわけではないことに注意。薬剤部門で調剤・払い出しを完了するための施設（たとえば病院）やシステムでのサポートに関する設定をしてもよい。</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
+    <t xml:space="preserve">ele-1:空のParametersリソースでない限り、すべてのFHIR要素には@valueまたはchildrenが必要です / All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
 </t>
   </si>
   <si>
@@ -1608,8 +1609,8 @@
 </t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+    <t>ele-1:空のParametersリソースでない限り、すべてのFHIR要素には@valueまたはchildrenが必要です / All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
+ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>MedicationRequest.dispenseRequest.extension:expectedRepeatCount</t>
@@ -1635,10 +1636,11 @@
 user contentmodifiers</t>
   </si>
   <si>
-    <t>Extensions that cannot be ignored even if unrecognized</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+    <t>認識されていなくても無視できない拡張機能 / Extensions that cannot be ignored even if unrecognized</t>
+  </si>
+  <si>
+    <t>要素の基本的な定義の一部ではなく、それが含まれている要素の理解、および/または含まれる要素の子孫の理解を変更するために使用される場合があります。通常、修飾子要素は否定または資格を提供します。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。アプリケーションの処理リソースは、修飾子拡張機能をチェックする必要があります。
+モディファイア拡張は、リソースまたはdomainResource上の要素の意味を変更してはなりません（修飾軸自体の意味を変更することはできません）。 / May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
@@ -1722,10 +1724,10 @@
     <t>このエレメントは処方の有効期間（処方が失効する日）を示す。</t>
   </si>
   <si>
-    <t>It reflects the prescribers' perspective for the validity of the prescription. Dispenses must not be made against the prescription outside of this period. The lower-bound of the Dispensing Window signifies the earliest date that the prescription can be filled for the first time. If an upper-bound is not specified then the Prescription is open-ended or will default to a stale-date based on regulations.</t>
-  </si>
-  <si>
-    <t>Indicates when the Prescription becomes valid, and when it ceases to be a dispensable Prescription.</t>
+    <t>それは、処方箋の妥当性に対する処方者の視点を反映しています。この期間以外の処方箋に対して分配してはなりません。分配ウィンドウの下限は、処方箋が初めて満たすことができる最も早い日付を意味します。上限が指定されていない場合、処方箋はオープンエンドであるか、規制に基づいて古い日付にデフォルトになります。 / It reflects the prescribers' perspective for the validity of the prescription. Dispenses must not be made against the prescription outside of this period. The lower-bound of the Dispensing Window signifies the earliest date that the prescription can be filled for the first time. If an upper-bound is not specified then the Prescription is open-ended or will default to a stale-date based on regulations.</t>
+  </si>
+  <si>
+    <t>処方箋がいつ有効になるか、そしてそれが不可欠な処方箋であることを停止することを示します。 / Indicates when the Prescription becomes valid, and when it ceases to be a dispensable Prescription.</t>
   </si>
   <si>
     <t>Message/Body/NewRx/MedicationPrescribed/Refills</t>
@@ -1777,7 +1779,7 @@
     <t>終了時刻は全ての日付・時刻に対応する。たとえば、2012-02-03T10:00:00は2012-02-03を終了時刻(end)の値とする期間を示す。</t>
   </si>
   <si>
-    <t>If the end of the period is missing, it means that the period is ongoing</t>
+    <t>期間の終了が欠落している場合、それは期間が進行中であることを意味します / If the end of the period is missing, it means that the period is ongoing</t>
   </si>
   <si>
     <t>Period.end</t>
@@ -1866,16 +1868,16 @@
 </t>
   </si>
   <si>
-    <t>Numerical value (with implicit precision)</t>
-  </si>
-  <si>
-    <t>The value of the measured amount. The value includes an implicit precision in the presentation of the value.</t>
-  </si>
-  <si>
-    <t>The implicit precision in the value should always be honored. Monetary values have their own rules for handling precision (refer to standard accounting text books).</t>
-  </si>
-  <si>
-    <t>Precision is handled implicitly in almost all cases of measurement.</t>
+    <t>数値（暗黙の精度を持つ） / Numerical value (with implicit precision)</t>
+  </si>
+  <si>
+    <t>測定量の値。値には、値の表示に暗黙の精度が含まれます。 / The value of the measured amount. The value includes an implicit precision in the presentation of the value.</t>
+  </si>
+  <si>
+    <t>値の暗黙の精度は常に尊重されるべきです。金銭的価値には、精度を処理するための独自のルールがあります（標準的な会計の教科書を参照）。 / The implicit precision in the value should always be honored. Monetary values have their own rules for handling precision (refer to standard accounting text books).</t>
+  </si>
+  <si>
+    <t>精度は、測定のほとんどすべての場合に暗黙的に処理されます。 / Precision is handled implicitly in almost all cases of measurement.</t>
   </si>
   <si>
     <t>Quantity.value</t>
@@ -1890,16 +1892,16 @@
     <t>MedicationRequest.dispenseRequest.expectedSupplyDuration.comparator</t>
   </si>
   <si>
-    <t>&lt; | &lt;= | &gt;= | &gt; - how to understand the value</t>
-  </si>
-  <si>
-    <t>How the value should be understood and represented - whether the actual value is greater or less than the stated value due to measurement issues; e.g. if the comparator is "&lt;" , then the real value is &lt; stated value.</t>
-  </si>
-  <si>
-    <t>Need a framework for handling measures where the value is &lt;5ug/L or &gt;400mg/L due to the limitations of measuring methodology.</t>
-  </si>
-  <si>
-    <t>If there is no comparator, then there is no modification of the value</t>
+    <t>&lt;|&lt;= |&gt; = |&gt;  - 値の比較方法 / &lt; | &lt;= | &gt;= | &gt; - how to understand the value</t>
+  </si>
+  <si>
+    <t>値をどのように理解し、表現する必要があるか - 測定の問題により実際の値が記載されている値よりも大きいか小さいかどうか。例えばコンパレータが「&lt;」の場合、実際の値は&lt;stated値です。 / How the value should be understood and represented - whether the actual value is greater or less than the stated value due to measurement issues; e.g. if the comparator is "&lt;" , then the real value is &lt; stated value.</t>
+  </si>
+  <si>
+    <t>測定方法の制限があるため、値が&lt;5ug/Lまたは&gt; 400mg/Lの測定値を処理するためのフレームワークが必要です。 / Need a framework for handling measures where the value is &lt;5ug/L or &gt;400mg/L due to the limitations of measuring methodology.</t>
+  </si>
+  <si>
+    <t>コンパレータがない場合、値の変更はありません / If there is no comparator, then there is no modification of the value</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/quantity-comparator|4.3.0</t>
@@ -1917,13 +1919,13 @@
     <t>MedicationRequest.dispenseRequest.expectedSupplyDuration.unit</t>
   </si>
   <si>
-    <t>Unit representation</t>
-  </si>
-  <si>
-    <t>A human-readable form of the unit.</t>
-  </si>
-  <si>
-    <t>There are many representations for units of measure and in many contexts, particular representations are fixed and required. I.e. mcg for micrograms.</t>
+    <t>ユニット表現 / Unit representation</t>
+  </si>
+  <si>
+    <t>ユニットの人間の読み取り可能な形式。 / A human-readable form of the unit.</t>
+  </si>
+  <si>
+    <t>測定単位には多くの表現があり、多くのコンテキストでは、特定の表現が固定され、必要です。すなわちマイクログラム用MCG。 / There are many representations for units of measure and in many contexts, particular representations are fixed and required. I.e. mcg for micrograms.</t>
   </si>
   <si>
     <t>日</t>
@@ -1941,13 +1943,13 @@
     <t>MedicationRequest.dispenseRequest.expectedSupplyDuration.system</t>
   </si>
   <si>
-    <t>System that defines coded unit form</t>
-  </si>
-  <si>
-    <t>The identification of the system that provides the coded form of the unit.</t>
-  </si>
-  <si>
-    <t>Need to know the system that defines the coded form of the unit.</t>
+    <t>コード化されたユニットフォームを定義するシステム / System that defines coded unit form</t>
+  </si>
+  <si>
+    <t>ユニットのコード化された形式を提供するシステムの識別。 / The identification of the system that provides the coded form of the unit.</t>
+  </si>
+  <si>
+    <t>ユニットのコード化された形式を定義するシステムを知る必要があります。 / Need to know the system that defines the coded form of the unit.</t>
   </si>
   <si>
     <t>http://unitsofmeasure.org</t>
@@ -1966,16 +1968,16 @@
     <t>MedicationRequest.dispenseRequest.expectedSupplyDuration.code</t>
   </si>
   <si>
-    <t>Coded form of the unit</t>
-  </si>
-  <si>
-    <t>A computer processable form of the unit in some unit representation system.</t>
-  </si>
-  <si>
-    <t>The preferred system is UCUM, but SNOMED CT can also be used (for customary units) or ISO 4217 for currency.  The context of use may additionally require a code from a particular system.</t>
-  </si>
-  <si>
-    <t>Need a computable form of the unit that is fixed across all forms. UCUM provides this for quantities, but SNOMED CT provides many units of interest.</t>
+    <t>ユニットのコード化された形式 / Coded form of the unit</t>
+  </si>
+  <si>
+    <t>一部のユニット表現システムのユニットのコンピューター処理可能な形式。 / A computer processable form of the unit in some unit representation system.</t>
+  </si>
+  <si>
+    <t>優先システムはUCUMですが、独自の単位にはSNOMED-CT、または通貨にISO 4217を使用することもできます。使用のコンテキストには、特定のシステムからのコードがさらに必要になる場合があります。 / The preferred system is UCUM, but SNOMED CT can also be used (for customary units) or ISO 4217 for currency.  The context of use may additionally require a code from a particular system.</t>
+  </si>
+  <si>
+    <t>すべてのフォームに固定されたユニットの計算可能な形式が必要です。UCUMはこれを数量で提供しますが、Snomed CTは多くの関心のある単位を提供します。 / Need a computable form of the unit that is fixed across all forms. UCUM provides this for quantities, but SNOMED CT provides many units of interest.</t>
   </si>
   <si>
     <t>d</t>
@@ -2058,7 +2060,7 @@
     <t>代替品の理由を表す一般的パターンに全てのターミノロジが適応しているわけではない。情報モデルはCodeableConceptではなく、直接Codingをを使用してテキストやコーディング、翻訳、そしてエレメントと事前条件、事後条件の関係について管理するためにその構造を提示する必要がある。</t>
   </si>
   <si>
-    <t>SubstanceAdminSubstitutionReason</t>
+    <t>物質投与代替理由 / SubstanceAdminSubstitutionReason</t>
   </si>
   <si>
     <t>http://terminology.hl7.org/ValueSet/v3-SubstanceAdminSubstitutionReason</t>
@@ -2465,7 +2467,7 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="83.6953125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="127.66796875" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="64.76953125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
